--- a/outputs/daily/hr_rankings_2026-08-03.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-03.xlsx
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>62.5</v>
+        <v>62.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>78.7</v>
+        <v>74.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Contact streak: 10/30 over last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Contact streak: 12/26 over last 7 games</t>
+          <t>Contact streak: 13/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -14487,24 +14487,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>2026-08-04T00:05:00Z</t>
@@ -14517,24 +14517,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Matthew Boyd</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>571510</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>47.4</v>
       </c>
@@ -14550,26 +14538,26 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>41.6</v>
+        <v>45.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>42</v>
+        <v>40.2</v>
       </c>
       <c r="R53" t="n">
         <v>29.8</v>
       </c>
       <c r="S53" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U53" t="n">
-        <v>74.90000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -14583,7 +14571,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -14608,7 +14596,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -14625,27 +14613,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -14655,99 +14643,75 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>100.6864</t>
+          <t>100.8957</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4263</t>
+          <t>0.4185</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1794</t>
+          <t>0.1993</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3216</t>
+          <t>0.3267</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.1706</t>
-        </is>
-      </c>
-      <c r="BA53" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="BB53" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="BC53" t="inlineStr">
-        <is>
-          <t>88.57</t>
-        </is>
-      </c>
-      <c r="BD53" t="inlineStr">
-        <is>
-          <t>0.4071</t>
-        </is>
-      </c>
-      <c r="BE53" t="inlineStr">
-        <is>
-          <t>0.158</t>
-        </is>
-      </c>
-      <c r="BF53" t="inlineStr">
-        <is>
-          <t>25.71</t>
-        </is>
-      </c>
+          <t>0.1931</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
       <c r="BG53" t="inlineStr"/>
       <c r="BH53" t="inlineStr"/>
       <c r="BI53" t="inlineStr">
@@ -14763,27 +14727,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -14793,14 +14757,26 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Bubba Chandler</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>696149</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L54" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -14814,26 +14790,26 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>45.1</v>
+        <v>38.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>40.2</v>
+        <v>35</v>
       </c>
       <c r="R54" t="n">
-        <v>29.8</v>
+        <v>27.6</v>
       </c>
       <c r="S54" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T54" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U54" t="n">
-        <v>4.2</v>
+        <v>48.5</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -14847,7 +14823,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -14872,7 +14848,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -14889,27 +14865,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -14919,80 +14895,104 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>100.8957</t>
+          <t>100.4645</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.4402</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1993</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3267</t>
+          <t>0.3448</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1931</t>
-        </is>
-      </c>
-      <c r="BA54" t="inlineStr"/>
-      <c r="BB54" t="inlineStr"/>
-      <c r="BC54" t="inlineStr"/>
-      <c r="BD54" t="inlineStr"/>
-      <c r="BE54" t="inlineStr"/>
-      <c r="BF54" t="inlineStr"/>
+          <t>0.1806</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>7.16</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>37.97</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>89.22</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>0.3779</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>0.1532</t>
+        </is>
+      </c>
+      <c r="BF54" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
       <c r="BG54" t="inlineStr"/>
       <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15003,27 +15003,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>691176</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jasson Dominguez</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-03T23:05:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15033,17 +15033,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15066,26 +15066,26 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>38.7</v>
+        <v>28.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>35</v>
+        <v>54.1</v>
       </c>
       <c r="R55" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S55" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U55" t="n">
-        <v>48.5</v>
+        <v>19.5</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
@@ -15151,17 +15151,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15171,104 +15171,104 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>100.4645</t>
+          <t>100.8799</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.4402</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3448</t>
+          <t>0.2976</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>74.35</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>44.58</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.06</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1806</t>
+          <t>0.1485</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.4864</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.1532</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr"/>
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15279,27 +15279,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jasson Dominguez</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-03T23:05:00Z</t>
+          <t>2026-08-04T00:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -15309,17 +15309,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15342,26 +15342,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>28.3</v>
+        <v>41.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>54.1</v>
+        <v>63.5</v>
       </c>
       <c r="R56" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S56" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T56" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U56" t="n">
-        <v>19.5</v>
+        <v>22.4</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.3% barrel, 7.3 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15447,104 +15447,104 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>100.8799</t>
+          <t>101.5766</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.1746</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.2976</t>
+          <t>0.3201</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>74.35</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>67.76</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>44.58</t>
+          <t>36.93</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1485</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.4864</t>
+          <t>0.5273</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr"/>
       <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -15555,27 +15555,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-04T00:10:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15590,21 +15590,21 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -15618,26 +15618,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>63.5</v>
+        <v>42</v>
       </c>
       <c r="R57" t="n">
-        <v>27.6</v>
+        <v>29.8</v>
       </c>
       <c r="S57" t="n">
         <v>59.8</v>
       </c>
       <c r="T57" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U57" t="n">
-        <v>22.4</v>
+        <v>68.7</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -15693,27 +15693,27 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.3% barrel, 7.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -15723,104 +15723,104 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.37</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>101.5766</t>
+          <t>100.6864</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.4263</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1746</t>
+          <t>0.1794</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3201</t>
+          <t>0.3216</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>36.93</t>
+          <t>32.68</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1706</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.5273</t>
+          <t>0.4071</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr"/>
       <c r="BH57" t="inlineStr"/>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -17464,7 +17464,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>78</v>
       </c>
       <c r="U64" t="n">
-        <v>14.6</v>
+        <v>10.8</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>75</v>
       </c>
       <c r="U73" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
@@ -22239,27 +22239,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>663494</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T23:05:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -22274,21 +22274,21 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -22302,26 +22302,26 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>34.6</v>
+        <v>22.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>42</v>
+        <v>35.4</v>
       </c>
       <c r="R82" t="n">
-        <v>29.8</v>
+        <v>38.2</v>
       </c>
       <c r="S82" t="n">
         <v>71.7</v>
       </c>
       <c r="T82" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U82" t="n">
-        <v>7</v>
+        <v>39.7</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
@@ -22377,12 +22377,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -22392,12 +22392,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Contact streak: 5/13 over last 7 games</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -22407,104 +22407,104 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>39.07</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>98.8948</t>
+          <t>96.7857</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.4214</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.3468</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.4071</t>
+          <t>0.3546</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr"/>
       <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -22515,27 +22515,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>663494</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-03T23:05:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -22550,17 +22550,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -22578,26 +22578,26 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>22.3</v>
+        <v>34.6</v>
       </c>
       <c r="Q83" t="n">
-        <v>35.4</v>
+        <v>42</v>
       </c>
       <c r="R83" t="n">
-        <v>38.2</v>
+        <v>29.8</v>
       </c>
       <c r="S83" t="n">
         <v>71.7</v>
       </c>
       <c r="T83" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>39.7</v>
+        <v>5.7</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr"/>
@@ -22653,12 +22653,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -22668,12 +22668,12 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Contact streak: 5/13 over last 7 games</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -22683,104 +22683,104 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>39.07</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>96.7857</t>
+          <t>98.8948</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.4214</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.1525</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>39.64</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.3546</t>
+          <t>0.4071</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr"/>
       <c r="BH83" t="inlineStr"/>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -35403,22 +35403,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>672613</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Eliezer Alfonzo</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -35433,26 +35433,14 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Matthew Boyd</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>571510</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -35466,26 +35454,26 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>10.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q131" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="R131" t="n">
-        <v>29.8</v>
+        <v>27.6</v>
       </c>
       <c r="S131" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T131" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U131" t="n">
-        <v>24.9</v>
+        <v>14.1</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -35499,7 +35487,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -35524,7 +35512,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -35541,7 +35529,7 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
@@ -35556,12 +35544,12 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
@@ -35571,104 +35559,80 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>97.1635</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>0.319</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>0.095</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="AP131" t="inlineStr">
-        <is>
-          <t>89.1</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>95.2764</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>0.271</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>0.074</t>
-        </is>
-      </c>
-      <c r="AT131" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>68.4</t>
-        </is>
-      </c>
-      <c r="AV131" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="AW131" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
+      <c r="AZ131" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="BA131" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="BB131" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="BC131" t="inlineStr">
-        <is>
-          <t>88.57</t>
-        </is>
-      </c>
-      <c r="BD131" t="inlineStr">
-        <is>
-          <t>0.4071</t>
-        </is>
-      </c>
-      <c r="BE131" t="inlineStr">
-        <is>
-          <t>0.158</t>
-        </is>
-      </c>
-      <c r="BF131" t="inlineStr">
-        <is>
-          <t>25.71</t>
-        </is>
-      </c>
+      <c r="BA131" t="inlineStr"/>
+      <c r="BB131" t="inlineStr"/>
+      <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
       <c r="BG131" t="inlineStr"/>
       <c r="BH131" t="inlineStr"/>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -35679,22 +35643,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>672613</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Eliezer Alfonzo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -35709,14 +35673,26 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Matthew Boyd</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>571510</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L132" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -35730,26 +35706,26 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>8.1</v>
+        <v>10.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="R132" t="n">
-        <v>27.6</v>
+        <v>29.8</v>
       </c>
       <c r="S132" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T132" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U132" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -35763,7 +35739,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -35788,7 +35764,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -35805,12 +35781,12 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -35820,12 +35796,12 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -35835,57 +35811,57 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>97.1635</t>
+          <t>95.2764</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.271</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -35895,20 +35871,44 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr"/>
-      <c r="BB132" t="inlineStr"/>
-      <c r="BC132" t="inlineStr"/>
-      <c r="BD132" t="inlineStr"/>
-      <c r="BE132" t="inlineStr"/>
-      <c r="BF132" t="inlineStr"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>88.57</t>
+        </is>
+      </c>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>0.4071</t>
+        </is>
+      </c>
+      <c r="BE132" t="inlineStr">
+        <is>
+          <t>0.158</t>
+        </is>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>25.71</t>
+        </is>
+      </c>
       <c r="BG132" t="inlineStr"/>
       <c r="BH132" t="inlineStr"/>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -38226,7 +38226,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>62.5</v>
+        <v>62.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>78.7</v>
+        <v>74.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-03.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-03.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ136"/>
+  <dimension ref="A1:BJ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27039,12 +27039,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>686668</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -27088,7 +27088,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>23.7</v>
+        <v>27.9</v>
       </c>
       <c r="Q99" t="n">
         <v>39.2</v>
@@ -27121,7 +27121,7 @@
         <v>78</v>
       </c>
       <c r="U99" t="n">
-        <v>29.4</v>
+        <v>5.7</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
@@ -27207,67 +27207,67 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>99.7114</t>
+          <t>98.8607</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.2624</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>37.19</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.0905</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -28419,27 +28419,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -28449,17 +28449,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -28468,7 +28468,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -28486,22 +28486,22 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>27.9</v>
+        <v>33</v>
       </c>
       <c r="Q104" t="n">
-        <v>39.2</v>
+        <v>23</v>
       </c>
       <c r="R104" t="n">
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="S104" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T104" t="n">
         <v>78</v>
       </c>
       <c r="U104" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -28557,134 +28557,134 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.93</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>98.8607</t>
+          <t>100.2229</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.4019</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.3237</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>40.62</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -28695,27 +28695,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>691458</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-03T23:05:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -28730,17 +28730,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -28758,26 +28758,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="Q105" t="n">
-        <v>23</v>
+        <v>35.4</v>
       </c>
       <c r="R105" t="n">
-        <v>34.3</v>
+        <v>38.2</v>
       </c>
       <c r="S105" t="n">
         <v>47.9</v>
       </c>
       <c r="T105" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U105" t="n">
-        <v>36</v>
+        <v>14.6</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -28838,22 +28838,22 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -28863,104 +28863,104 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>100.2229</t>
+          <t>99.9253</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.4019</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3237</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>40.62</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.3546</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr"/>
       <c r="BH105" t="inlineStr"/>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -28971,12 +28971,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>691458</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -29001,7 +29001,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -29020,7 +29020,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29034,11 +29034,11 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>33.2</v>
+        <v>17.9</v>
       </c>
       <c r="Q106" t="n">
         <v>35.4</v>
@@ -29047,13 +29047,13 @@
         <v>38.2</v>
       </c>
       <c r="S106" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U106" t="n">
-        <v>14.6</v>
+        <v>21.5</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr"/>
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -29124,12 +29124,12 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -29139,67 +29139,67 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>35.06</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>99.9253</t>
+          <t>98.1248</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1151</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2729</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.1081</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
@@ -29247,27 +29247,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-03T23:05:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -29277,24 +29277,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>693645</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
         <v>36.8</v>
       </c>
@@ -29310,26 +29298,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>17.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q107" t="n">
-        <v>35.4</v>
+        <v>41.2</v>
       </c>
       <c r="R107" t="n">
-        <v>38.2</v>
+        <v>29.8</v>
       </c>
       <c r="S107" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T107" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U107" t="n">
-        <v>21.5</v>
+        <v>81.7</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -29343,7 +29331,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -29368,7 +29356,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -29385,27 +29373,27 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -29415,104 +29403,80 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>29.04</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>86.28</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>98.1248</t>
+          <t>96.3021</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3805</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>0.1151</t>
+          <t>0.0836</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.2729</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>0.1081</t>
-        </is>
-      </c>
-      <c r="BA107" t="inlineStr">
-        <is>
-          <t>7.99</t>
-        </is>
-      </c>
-      <c r="BB107" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
-      </c>
-      <c r="BC107" t="inlineStr">
-        <is>
-          <t>88.44</t>
-        </is>
-      </c>
-      <c r="BD107" t="inlineStr">
-        <is>
-          <t>0.3546</t>
-        </is>
-      </c>
-      <c r="BE107" t="inlineStr">
-        <is>
-          <t>0.1372</t>
-        </is>
-      </c>
-      <c r="BF107" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
-      </c>
+          <t>0.0977</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr"/>
+      <c r="BB107" t="inlineStr"/>
+      <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
       <c r="BG107" t="inlineStr"/>
       <c r="BH107" t="inlineStr"/>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr"/>
@@ -29523,27 +29487,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Tyler Freeman</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-04T00:40:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -29553,14 +29517,26 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Ian Seymour</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>693855</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L108" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -29574,26 +29550,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>8.699999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="Q108" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
       <c r="R108" t="n">
-        <v>29.8</v>
+        <v>38.7</v>
       </c>
       <c r="S108" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T108" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U108" t="n">
-        <v>81.7</v>
+        <v>12</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -29607,7 +29583,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -29632,7 +29608,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr"/>
@@ -29649,110 +29625,134 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>86.28</t>
+          <t>88.42</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>96.3021</t>
+          <t>98.7495</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.3805</t>
+          <t>0.3572</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.0836</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3152</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>70.74</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.0977</t>
-        </is>
-      </c>
-      <c r="BA108" t="inlineStr"/>
-      <c r="BB108" t="inlineStr"/>
-      <c r="BC108" t="inlineStr"/>
-      <c r="BD108" t="inlineStr"/>
-      <c r="BE108" t="inlineStr"/>
-      <c r="BF108" t="inlineStr"/>
+          <t>0.0723</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>8.78</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>37.1</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>88.63</t>
+        </is>
+      </c>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>0.3721</t>
+        </is>
+      </c>
+      <c r="BE108" t="inlineStr">
+        <is>
+          <t>0.1551</t>
+        </is>
+      </c>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
+      </c>
       <c r="BG108" t="inlineStr"/>
       <c r="BH108" t="inlineStr"/>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -29763,12 +29763,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>671289</t>
+          <t>681198</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tyler Freeman</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -29793,7 +29793,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -29826,11 +29826,11 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>15.8</v>
+        <v>12.6</v>
       </c>
       <c r="Q109" t="n">
         <v>39.2</v>
@@ -29839,13 +29839,13 @@
         <v>38.7</v>
       </c>
       <c r="S109" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T109" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U109" t="n">
-        <v>12</v>
+        <v>18.2</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -29884,7 +29884,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr"/>
@@ -29901,12 +29901,12 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -29916,12 +29916,12 @@
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 7/29, 0 HR</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -29931,67 +29931,67 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>88.42</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>98.7495</t>
+          <t>96.1088</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.3572</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3152</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>70.74</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.0723</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
@@ -30039,27 +30039,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>681198</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-04T01:40:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -30069,22 +30069,22 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -30106,22 +30106,22 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>12.6</v>
+        <v>26.6</v>
       </c>
       <c r="Q110" t="n">
-        <v>39.2</v>
+        <v>45.9</v>
       </c>
       <c r="R110" t="n">
-        <v>38.7</v>
+        <v>28.2</v>
       </c>
       <c r="S110" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T110" t="n">
         <v>50</v>
       </c>
       <c r="U110" t="n">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr"/>
@@ -30177,12 +30177,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -30192,119 +30192,119 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>38.92</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>96.1088</t>
+          <t>99.74</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.3186</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1091</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr"/>
       <c r="BH110" t="inlineStr"/>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -30315,27 +30315,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-04T01:40:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -30345,17 +30345,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>687075</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -30364,7 +30364,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -30378,26 +30378,26 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>26.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q111" t="n">
-        <v>45.9</v>
+        <v>36.5</v>
       </c>
       <c r="R111" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S111" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T111" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U111" t="n">
-        <v>19.5</v>
+        <v>45.3</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -30453,27 +30453,27 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 9/30, 1 HR</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
@@ -30483,104 +30483,104 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>38.92</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>99.74</t>
+          <t>96.4016</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.3297</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.0745</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>0.3186</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>67.44</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>0.1091</t>
+          <t>0.0748</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.3962</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr"/>
       <c r="BH111" t="inlineStr"/>
       <c r="BI111" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ111" t="inlineStr"/>
@@ -30591,12 +30591,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>694378</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Jacob Gonzalez</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -30654,26 +30654,26 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>5.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q112" t="n">
-        <v>36.5</v>
+        <v>37.8</v>
       </c>
       <c r="R112" t="n">
         <v>27.6</v>
       </c>
       <c r="S112" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T112" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U112" t="n">
-        <v>45.3</v>
+        <v>10.6</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -30729,27 +30729,27 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 1 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -30759,67 +30759,67 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>96.4016</t>
+          <t>99.3194</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.0745</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>67.44</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.0748</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
@@ -30867,27 +30867,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>694378</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jacob Gonzalez</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -30897,26 +30897,26 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>687075</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>36</v>
+        <v>35.2</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -30930,26 +30930,26 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>25.3</v>
+        <v>27.5</v>
       </c>
       <c r="Q113" t="n">
-        <v>37.8</v>
+        <v>23</v>
       </c>
       <c r="R113" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S113" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T113" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U113" t="n">
-        <v>10.6</v>
+        <v>52.8</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr"/>
@@ -31005,27 +31005,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -31035,104 +31035,104 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.3194</t>
+          <t>98.5788</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4014</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1432</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1487</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr"/>
       <c r="BH113" t="inlineStr"/>
       <c r="BI113" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ113" t="inlineStr"/>
@@ -31143,27 +31143,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Jose Caballero</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-03T23:05:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -31173,26 +31173,26 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -31210,22 +31210,22 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>27.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q114" t="n">
-        <v>23</v>
+        <v>55.6</v>
       </c>
       <c r="R114" t="n">
-        <v>34.3</v>
+        <v>38.2</v>
       </c>
       <c r="S114" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T114" t="n">
         <v>50</v>
       </c>
       <c r="U114" t="n">
-        <v>52.8</v>
+        <v>43.2</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -31281,12 +31281,12 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -31296,12 +31296,12 @@
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -31311,104 +31311,104 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>84.46</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>98.5788</t>
+          <t>96.3388</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.4014</t>
+          <t>0.3362</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.1432</t>
+          <t>0.1087</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.2836</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4864</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr"/>
       <c r="BH114" t="inlineStr"/>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -31419,24 +31419,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>676609</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jose Caballero</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>2026-08-03T23:05:00Z</t>
@@ -31449,17 +31449,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -31468,7 +31468,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -31486,22 +31486,22 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="Q115" t="n">
-        <v>55.6</v>
+        <v>35.4</v>
       </c>
       <c r="R115" t="n">
         <v>38.2</v>
       </c>
       <c r="S115" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T115" t="n">
         <v>50</v>
       </c>
       <c r="U115" t="n">
-        <v>43.2</v>
+        <v>25.8</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -31557,27 +31557,27 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -31587,97 +31587,97 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>84.46</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>96.3388</t>
+          <t>98.6916</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.3362</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.2836</t>
+          <t>0.2965</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.4864</t>
+          <t>0.3546</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
@@ -31695,27 +31695,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-03T23:05:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -31725,17 +31725,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -31758,26 +31758,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>15</v>
+        <v>19.4</v>
       </c>
       <c r="Q116" t="n">
-        <v>35.4</v>
+        <v>34.2</v>
       </c>
       <c r="R116" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S116" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T116" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U116" t="n">
-        <v>25.8</v>
+        <v>21.1</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -31816,7 +31816,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -31833,12 +31833,12 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -31848,12 +31848,12 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -31863,27 +31863,27 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>98.6916</t>
+          <t>98.1872</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -31893,74 +31893,74 @@
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.2965</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>15.42</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>39.64</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3546</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -31971,27 +31971,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:40:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -32006,12 +32006,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32038,13 +32038,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>19.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q117" t="n">
-        <v>34.2</v>
+        <v>51.1</v>
       </c>
       <c r="R117" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S117" t="n">
         <v>59.8</v>
@@ -32053,7 +32053,7 @@
         <v>75</v>
       </c>
       <c r="U117" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -32109,12 +32109,12 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -32124,12 +32124,12 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 0/14, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32139,104 +32139,104 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>85.67</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>98.1872</t>
+          <t>95.3063</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.2663</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.0759</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.2491</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.4664</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1532</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -32247,27 +32247,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -32277,17 +32277,17 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>687075</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -32296,7 +32296,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -32310,26 +32310,26 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>5.3</v>
+        <v>16.6</v>
       </c>
       <c r="Q118" t="n">
-        <v>51.1</v>
+        <v>37.8</v>
       </c>
       <c r="R118" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="S118" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T118" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -32385,27 +32385,27 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/14, 0 HR</t>
+          <t>Last 7 games: 9/30, 0 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -32415,104 +32415,104 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>85.67</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>95.3063</t>
+          <t>98.3176</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.2663</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.0759</t>
+          <t>0.1084</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.2491</t>
+          <t>0.3134</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.0957</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.4664</t>
+          <t>0.3962</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr"/>
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -32523,27 +32523,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>665804</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Miguel Amaya</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -32553,26 +32553,14 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Brandon Sproat</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>687075</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -32590,19 +32578,19 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>16.6</v>
+        <v>22</v>
       </c>
       <c r="Q119" t="n">
-        <v>37.8</v>
+        <v>41.2</v>
       </c>
       <c r="R119" t="n">
-        <v>27.6</v>
+        <v>29.8</v>
       </c>
       <c r="S119" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T119" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U119" t="n">
         <v>27</v>
@@ -32619,7 +32607,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -32644,7 +32632,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -32661,12 +32649,12 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -32676,12 +32664,12 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -32691,104 +32679,80 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>87.03</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>98.3176</t>
+          <t>97.668</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3412</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.1084</t>
+          <t>0.1224</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>70.87</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.0957</t>
-        </is>
-      </c>
-      <c r="BA119" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>89.3</t>
-        </is>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>0.3962</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
-        <is>
-          <t>0.1472</t>
-        </is>
-      </c>
-      <c r="BF119" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
+          <t>0.1469</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -32799,27 +32763,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>665804</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-04T01:40:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -32832,9 +32796,21 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Brandon Pfaadt</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>694297</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L120" t="n">
         <v>34</v>
       </c>
@@ -32854,22 +32830,22 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q120" t="n">
-        <v>41.2</v>
+        <v>45.9</v>
       </c>
       <c r="R120" t="n">
-        <v>29.8</v>
+        <v>28.2</v>
       </c>
       <c r="S120" t="n">
         <v>40.2</v>
       </c>
       <c r="T120" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U120" t="n">
-        <v>27</v>
+        <v>34.2</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -32908,7 +32884,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -32925,12 +32901,12 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -32940,12 +32916,12 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -32955,80 +32931,104 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>87.03</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>97.668</t>
+          <t>99.3149</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3412</t>
+          <t>0.3088</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.1224</t>
+          <t>0.1057</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>18.12</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.1469</t>
-        </is>
-      </c>
-      <c r="BA120" t="inlineStr"/>
-      <c r="BB120" t="inlineStr"/>
-      <c r="BC120" t="inlineStr"/>
-      <c r="BD120" t="inlineStr"/>
-      <c r="BE120" t="inlineStr"/>
-      <c r="BF120" t="inlineStr"/>
+          <t>0.1372</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>39.78</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>0.4275</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
       <c r="BG120" t="inlineStr"/>
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -33039,27 +33039,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-04T01:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -33069,17 +33069,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -33088,7 +33088,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>34</v>
+        <v>33.7</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -33102,26 +33102,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Q121" t="n">
-        <v>45.9</v>
+        <v>50.7</v>
       </c>
       <c r="R121" t="n">
-        <v>28.2</v>
+        <v>34.3</v>
       </c>
       <c r="S121" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T121" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U121" t="n">
-        <v>34.2</v>
+        <v>10.1</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -33177,12 +33177,12 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -33192,12 +33192,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -33207,82 +33207,82 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>84.01</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>99.3149</t>
+          <t>95.6367</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.3088</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.0813</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.2996</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>43.56</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.0925</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
@@ -33292,19 +33292,19 @@
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1794</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -33315,27 +33315,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -33345,26 +33345,14 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Aaron Nola</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>605400</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
-        <v>33.7</v>
+        <v>32.4</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -33378,26 +33366,26 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="Q122" t="n">
-        <v>50.7</v>
+        <v>41.2</v>
       </c>
       <c r="R122" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S122" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U122" t="n">
-        <v>10.1</v>
+        <v>14.1</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -33411,7 +33399,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -33436,7 +33424,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr"/>
@@ -33458,7 +33446,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -33468,12 +33456,12 @@
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -33483,104 +33471,80 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>84.01</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>95.6367</t>
+          <t>96.8228</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.0813</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.2996</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.0925</t>
-        </is>
-      </c>
-      <c r="BA122" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="BB122" t="inlineStr">
-        <is>
-          <t>41.83</t>
-        </is>
-      </c>
-      <c r="BC122" t="inlineStr">
-        <is>
-          <t>88.84</t>
-        </is>
-      </c>
-      <c r="BD122" t="inlineStr">
-        <is>
-          <t>0.4275</t>
-        </is>
-      </c>
-      <c r="BE122" t="inlineStr">
-        <is>
-          <t>0.1794</t>
-        </is>
-      </c>
-      <c r="BF122" t="inlineStr">
-        <is>
-          <t>27.53</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr"/>
+      <c r="BB122" t="inlineStr"/>
+      <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
       <c r="BG122" t="inlineStr"/>
       <c r="BH122" t="inlineStr"/>
       <c r="BI122" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ122" t="inlineStr"/>
@@ -33591,24 +33555,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>2026-08-04T00:05:00Z</t>
@@ -33621,14 +33585,26 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Logan Webb</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>657277</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L123" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -33646,22 +33622,22 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>6.6</v>
+        <v>19.3</v>
       </c>
       <c r="Q123" t="n">
-        <v>41.2</v>
+        <v>30.6</v>
       </c>
       <c r="R123" t="n">
         <v>27.6</v>
       </c>
       <c r="S123" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T123" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U123" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -33675,7 +33651,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -33700,7 +33676,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr"/>
@@ -33717,27 +33693,27 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
@@ -33747,75 +33723,99 @@
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>96.8228</t>
+          <t>98.5554</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.3531</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.1132</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.2862</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA123" t="inlineStr"/>
-      <c r="BB123" t="inlineStr"/>
-      <c r="BC123" t="inlineStr"/>
-      <c r="BD123" t="inlineStr"/>
-      <c r="BE123" t="inlineStr"/>
-      <c r="BF123" t="inlineStr"/>
+          <t>0.1411</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>39.57</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>88.79</t>
+        </is>
+      </c>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>0.3826</t>
+        </is>
+      </c>
+      <c r="BE123" t="inlineStr">
+        <is>
+          <t>0.1289</t>
+        </is>
+      </c>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
       <c r="BG123" t="inlineStr"/>
       <c r="BH123" t="inlineStr"/>
       <c r="BI123" t="inlineStr">
@@ -33831,12 +33831,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -33861,7 +33861,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -33898,7 +33898,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>19.3</v>
+        <v>24</v>
       </c>
       <c r="Q124" t="n">
         <v>30.6</v>
@@ -33907,13 +33907,13 @@
         <v>27.6</v>
       </c>
       <c r="S124" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T124" t="n">
         <v>50</v>
       </c>
       <c r="U124" t="n">
-        <v>30.3</v>
+        <v>33.7</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -33969,12 +33969,12 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -33984,7 +33984,7 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 4/18, 1 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
@@ -33999,67 +33999,67 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>98.5554</t>
+          <t>99.3532</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3531</t>
+          <t>0.3543</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.1132</t>
+          <t>0.1264</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.2862</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.22</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
@@ -34107,27 +34107,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -34137,26 +34137,26 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -34170,26 +34170,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>24</v>
+        <v>7.1</v>
       </c>
       <c r="Q125" t="n">
-        <v>30.6</v>
+        <v>23</v>
       </c>
       <c r="R125" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S125" t="n">
-        <v>47.9</v>
+        <v>95.5</v>
       </c>
       <c r="T125" t="n">
         <v>50</v>
       </c>
       <c r="U125" t="n">
-        <v>33.7</v>
+        <v>27</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -34245,27 +34245,27 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 1 HR</t>
+          <t>Last 7 games: 9/30, 0 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -34275,104 +34275,104 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>19.22</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>99.3532</t>
+          <t>94.0255</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.3543</t>
+          <t>0.3693</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.1264</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.3037</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>27.19</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.1112</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr"/>
       <c r="BH125" t="inlineStr"/>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -34383,27 +34383,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:10:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -34413,26 +34413,26 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -34446,26 +34446,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>23</v>
+        <v>47.1</v>
       </c>
       <c r="R126" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S126" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T126" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U126" t="n">
-        <v>27</v>
+        <v>29.4</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -34521,12 +34521,12 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
@@ -34536,119 +34536,119 @@
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 0 HR</t>
+          <t>Last 7 games: 6/19, 0 HR</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>19.22</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>94.0255</t>
+          <t>95.8276</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.3693</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.0957</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3037</t>
+          <t>0.2807</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>68.39</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1112</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr"/>
       <c r="BH126" t="inlineStr"/>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -34659,27 +34659,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-04T00:10:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -34689,26 +34689,14 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Cristian Javier</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>664299</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -34722,26 +34710,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>7.2</v>
+        <v>13.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>47.1</v>
+        <v>41.2</v>
       </c>
       <c r="R127" t="n">
         <v>27.6</v>
       </c>
       <c r="S127" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T127" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U127" t="n">
-        <v>29.4</v>
+        <v>28.9</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -34755,7 +34743,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -34780,7 +34768,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr"/>
@@ -34797,12 +34785,12 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
@@ -34812,119 +34800,95 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 5/16, 0 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>86.25</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>95.8276</t>
+          <t>97.7864</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.3479</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.0957</t>
+          <t>0.1041</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.2807</t>
+          <t>0.2973</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1149</t>
-        </is>
-      </c>
-      <c r="BA127" t="inlineStr">
-        <is>
-          <t>9.72</t>
-        </is>
-      </c>
-      <c r="BB127" t="inlineStr">
-        <is>
-          <t>39.28</t>
-        </is>
-      </c>
-      <c r="BC127" t="inlineStr">
-        <is>
-          <t>90.3</t>
-        </is>
-      </c>
-      <c r="BD127" t="inlineStr">
-        <is>
-          <t>0.3998</t>
-        </is>
-      </c>
-      <c r="BE127" t="inlineStr">
-        <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BF127" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
+          <t>0.1285</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr"/>
+      <c r="BB127" t="inlineStr"/>
+      <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
       <c r="BG127" t="inlineStr"/>
       <c r="BH127" t="inlineStr"/>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -34935,27 +34899,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>683083</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Nasim Nunez</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -34965,14 +34929,26 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L128" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -34986,26 +34962,26 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>13.3</v>
+        <v>5</v>
       </c>
       <c r="Q128" t="n">
-        <v>41.2</v>
+        <v>49</v>
       </c>
       <c r="R128" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S128" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T128" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U128" t="n">
-        <v>28.9</v>
+        <v>0.8</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -35019,7 +34995,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -35044,7 +35020,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr"/>
@@ -35061,12 +35037,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
@@ -35076,12 +35052,12 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 0 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -35091,80 +35067,104 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>27.57</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>86.25</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>97.7864</t>
+          <t>95.8969</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.3479</t>
+          <t>0.3033</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1041</t>
+          <t>0.0734</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.2973</t>
+          <t>0.2792</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>18.12</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1285</t>
-        </is>
-      </c>
-      <c r="BA128" t="inlineStr"/>
-      <c r="BB128" t="inlineStr"/>
-      <c r="BC128" t="inlineStr"/>
-      <c r="BD128" t="inlineStr"/>
-      <c r="BE128" t="inlineStr"/>
-      <c r="BF128" t="inlineStr"/>
+          <t>0.0797</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>41.83</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>88.84</t>
+        </is>
+      </c>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>0.4275</t>
+        </is>
+      </c>
+      <c r="BE128" t="inlineStr">
+        <is>
+          <t>0.1794</t>
+        </is>
+      </c>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
       <c r="BG128" t="inlineStr"/>
       <c r="BH128" t="inlineStr"/>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -35175,27 +35175,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>683083</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nasim Nunez</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -35205,17 +35205,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -35224,7 +35224,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -35238,26 +35238,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>5</v>
+        <v>16.1</v>
       </c>
       <c r="Q129" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="R129" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S129" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T129" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U129" t="n">
-        <v>0.8</v>
+        <v>32</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -35296,7 +35296,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -35313,12 +35313,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -35328,12 +35328,12 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -35343,104 +35343,104 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>27.57</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>95.8969</t>
+          <t>97.1628</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3033</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.0734</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.2792</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.0797</t>
+          <t>0.102</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1794</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr"/>
       <c r="BH129" t="inlineStr"/>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -35451,27 +35451,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:10:00Z</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -35481,17 +35481,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -35518,22 +35518,22 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>16.1</v>
+        <v>6</v>
       </c>
       <c r="Q130" t="n">
-        <v>35</v>
+        <v>47.1</v>
       </c>
       <c r="R130" t="n">
         <v>27.6</v>
       </c>
       <c r="S130" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T130" t="n">
         <v>50</v>
       </c>
       <c r="U130" t="n">
-        <v>32</v>
+        <v>7.9</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -35589,12 +35589,12 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -35604,119 +35604,119 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 5/29, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>85.34</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>97.1628</t>
+          <t>94.8467</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.3415</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>0.0881</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.1532</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr"/>
       <c r="BH130" t="inlineStr"/>
       <c r="BI130" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ130" t="inlineStr"/>
@@ -35727,27 +35727,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-04T00:10:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -35757,17 +35757,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -35776,7 +35776,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -35790,26 +35790,26 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>6</v>
+        <v>12.3</v>
       </c>
       <c r="Q131" t="n">
-        <v>47.1</v>
+        <v>35</v>
       </c>
       <c r="R131" t="n">
         <v>27.6</v>
       </c>
       <c r="S131" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T131" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U131" t="n">
-        <v>7.9</v>
+        <v>19.5</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -35870,7 +35870,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -35880,119 +35880,119 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>85.34</t>
+          <t>86.88</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>94.8467</t>
+          <t>96.9916</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3415</t>
+          <t>0.3064</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.0881</t>
+          <t>0.0988</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2663</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr"/>
       <c r="BH131" t="inlineStr"/>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -36003,27 +36003,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>683766</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -36033,26 +36033,14 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Bubba Chandler</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>696149</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -36066,26 +36054,26 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>12.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>35</v>
+        <v>41.2</v>
       </c>
       <c r="R132" t="n">
         <v>27.6</v>
       </c>
       <c r="S132" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T132" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U132" t="n">
-        <v>19.5</v>
+        <v>10.6</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -36099,7 +36087,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -36124,7 +36112,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -36141,12 +36129,12 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -36156,12 +36144,12 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -36171,104 +36159,80 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>86.88</t>
+          <t>84.66</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>96.9916</t>
+          <t>96.0366</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.3064</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.0988</t>
+          <t>0.0718</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.2663</t>
+          <t>0.2389</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr">
-        <is>
-          <t>7.16</t>
-        </is>
-      </c>
-      <c r="BB132" t="inlineStr">
-        <is>
-          <t>37.97</t>
-        </is>
-      </c>
-      <c r="BC132" t="inlineStr">
-        <is>
-          <t>89.22</t>
-        </is>
-      </c>
-      <c r="BD132" t="inlineStr">
-        <is>
-          <t>0.3779</t>
-        </is>
-      </c>
-      <c r="BE132" t="inlineStr">
-        <is>
-          <t>0.1532</t>
-        </is>
-      </c>
-      <c r="BF132" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
-      </c>
+          <t>0.0473</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr"/>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
       <c r="BG132" t="inlineStr"/>
       <c r="BH132" t="inlineStr"/>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -36279,27 +36243,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>683766</t>
+          <t>691373</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Jhostynxon Garcia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -36309,14 +36273,26 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Brandon Sproat</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>687075</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L133" t="n">
-        <v>30.1</v>
+        <v>27.8</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -36334,22 +36310,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>5.4</v>
+        <v>13.4</v>
       </c>
       <c r="Q133" t="n">
-        <v>41.2</v>
+        <v>37.8</v>
       </c>
       <c r="R133" t="n">
         <v>27.6</v>
       </c>
       <c r="S133" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T133" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U133" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -36363,7 +36339,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -36388,7 +36364,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr"/>
@@ -36405,12 +36381,12 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
@@ -36420,12 +36396,12 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -36435,80 +36411,104 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>84.66</t>
+          <t>86.41</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>96.0366</t>
+          <t>97.4476</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2955</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.0718</t>
+          <t>0.0753</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2389</t>
+          <t>0.2698</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.0473</t>
-        </is>
-      </c>
-      <c r="BA133" t="inlineStr"/>
-      <c r="BB133" t="inlineStr"/>
-      <c r="BC133" t="inlineStr"/>
-      <c r="BD133" t="inlineStr"/>
-      <c r="BE133" t="inlineStr"/>
-      <c r="BF133" t="inlineStr"/>
+          <t>0.0583</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>41.61</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>0.3962</t>
+        </is>
+      </c>
+      <c r="BE133" t="inlineStr">
+        <is>
+          <t>0.1472</t>
+        </is>
+      </c>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
       <c r="BG133" t="inlineStr"/>
       <c r="BH133" t="inlineStr"/>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -36519,27 +36519,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>691373</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jhostynxon Garcia</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -36554,21 +36554,21 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>687075</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -36586,13 +36586,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>13.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q134" t="n">
-        <v>37.8</v>
+        <v>23</v>
       </c>
       <c r="R134" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S134" t="n">
         <v>40.2</v>
@@ -36601,7 +36601,7 @@
         <v>50</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -36657,12 +36657,12 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -36672,12 +36672,12 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -36687,104 +36687,104 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>86.41</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>97.4476</t>
+          <t>97.595</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.2955</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.0753</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.2698</t>
+          <t>0.278</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.0583</t>
+          <t>0.082</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr"/>
       <c r="BH134" t="inlineStr"/>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr"/>
@@ -36795,27 +36795,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -36830,21 +36830,21 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -36858,26 +36858,26 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="Q135" t="n">
-        <v>23</v>
+        <v>30.6</v>
       </c>
       <c r="R135" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S135" t="n">
         <v>40.2</v>
       </c>
       <c r="T135" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U135" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr"/>
@@ -36933,12 +36933,12 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -36948,12 +36948,12 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -36963,383 +36963,107 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>28.17</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.66</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>97.595</t>
+          <t>95.4793</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.2648</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.0398</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.2568</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>66.58</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.0259</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
       <c r="BH135" t="inlineStr"/>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>670032</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Nicky Lopez</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-08-04T00:05:00Z</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Logan Webb</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>657277</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P136" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R136" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S136" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="T136" t="n">
-        <v>80</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>H:2026/2025 P:2026/2025</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr"/>
-      <c r="AE136" t="inlineStr"/>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>Direct BvP not yet weighted; 2026/2025 Statcast baseline active</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>28.17</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>84.66</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>95.4793</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>0.2648</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>0.0398</t>
-        </is>
-      </c>
-      <c r="AT136" t="inlineStr">
-        <is>
-          <t>0.2568</t>
-        </is>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>66.58</t>
-        </is>
-      </c>
-      <c r="AV136" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="AW136" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>0.0259</t>
-        </is>
-      </c>
-      <c r="BA136" t="inlineStr">
-        <is>
-          <t>6.41</t>
-        </is>
-      </c>
-      <c r="BB136" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
-      </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>88.79</t>
-        </is>
-      </c>
-      <c r="BD136" t="inlineStr">
-        <is>
-          <t>0.3826</t>
-        </is>
-      </c>
-      <c r="BE136" t="inlineStr">
-        <is>
-          <t>0.1289</t>
-        </is>
-      </c>
-      <c r="BF136" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
-      <c r="BG136" t="inlineStr"/>
-      <c r="BH136" t="inlineStr"/>
-      <c r="BI136" t="inlineStr">
-        <is>
-          <t>Globe Life Field</t>
-        </is>
-      </c>
-      <c r="BJ136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/daily/hr_rankings_2026-08-03.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-03.xlsx
@@ -20343,56 +20343,56 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>621438</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Tyrone Taylor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20406,26 +20406,26 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>38.3</v>
+        <v>34.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>53.1</v>
+        <v>42</v>
       </c>
       <c r="R72" t="n">
-        <v>38.7</v>
+        <v>51.8</v>
       </c>
       <c r="S72" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T72" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -20481,27 +20481,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20511,104 +20511,112 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>87.41</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>100.285</t>
+          <t>98.8149</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.4003</t>
+          <t>0.4158</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1777</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3057</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>71.28</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>31.19</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.1952</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.4664</t>
+          <t>0.4101</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1507</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>25.59</t>
-        </is>
-      </c>
-      <c r="BG72" t="inlineStr"/>
-      <c r="BH72" t="inlineStr"/>
+          <t>28.14</t>
+        </is>
+      </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20619,56 +20627,56 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-04T00:40:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20682,58 +20690,62 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>25.3</v>
+        <v>38.3</v>
       </c>
       <c r="Q73" t="n">
-        <v>41</v>
+        <v>53.1</v>
       </c>
       <c r="R73" t="n">
-        <v>51.8</v>
+        <v>38.7</v>
       </c>
       <c r="S73" t="n">
-        <v>96.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T73" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20753,12 +20765,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -20768,12 +20780,12 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -20783,112 +20795,104 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
+          <t>9.13</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>40.87</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>89.56</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>100.285</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>0.4003</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>0.169</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>0.3172</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>73.58</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>31.83</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>42.69</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>28.87</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
           <t>5.9</t>
         </is>
       </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>38.57</t>
-        </is>
-      </c>
-      <c r="AP73" t="inlineStr">
-        <is>
-          <t>88.65</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>100.1181</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>0.4117</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>0.1188</t>
-        </is>
-      </c>
-      <c r="AT73" t="inlineStr">
-        <is>
-          <t>0.3441</t>
-        </is>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>70.38</t>
-        </is>
-      </c>
-      <c r="AV73" t="inlineStr">
-        <is>
-          <t>10.71</t>
-        </is>
-      </c>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>44.77</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1952</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.4071</t>
+          <t>0.4664</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>25.71</t>
-        </is>
-      </c>
-      <c r="BG73" t="inlineStr">
-        <is>
-          <t>R To L</t>
-        </is>
-      </c>
-      <c r="BH73" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>25.59</t>
+        </is>
+      </c>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20899,22 +20903,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>669394</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -20929,22 +20933,22 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -20962,26 +20966,26 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>48.7</v>
+        <v>25.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>30.6</v>
+        <v>41</v>
       </c>
       <c r="R74" t="n">
-        <v>41.1</v>
+        <v>51.8</v>
       </c>
       <c r="S74" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T74" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
-        <v>34.9</v>
+        <v>6</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -20995,7 +20999,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -21033,27 +21037,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -21063,112 +21067,112 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>102.6779</t>
+          <t>100.1181</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.1879</t>
+          <t>0.1188</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.3072</t>
+          <t>0.3441</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>75.23</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.1844</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.4071</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -21179,27 +21183,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>669394</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -21209,17 +21213,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -21228,7 +21232,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21242,62 +21246,58 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Projected Lineup, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>16.1</v>
+        <v>48.7</v>
       </c>
       <c r="Q75" t="n">
-        <v>49</v>
+        <v>30.6</v>
       </c>
       <c r="R75" t="n">
-        <v>71.3</v>
+        <v>41.1</v>
       </c>
       <c r="S75" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T75" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>2.5</v>
+        <v>34.9</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21317,27 +21317,27 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -21347,112 +21347,112 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>97.5962</t>
+          <t>102.6779</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.3496</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.1879</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.2744</t>
+          <t>0.3072</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>67.29</t>
+          <t>75.23</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>54.54</t>
+          <t>42.79</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.1844</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1794</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21463,56 +21463,56 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21526,26 +21526,26 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>24.7</v>
+        <v>16.1</v>
       </c>
       <c r="Q76" t="n">
-        <v>39.2</v>
+        <v>49</v>
       </c>
       <c r="R76" t="n">
-        <v>38.7</v>
+        <v>71.3</v>
       </c>
       <c r="S76" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T76" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U76" t="n">
-        <v>43.4</v>
+        <v>2.5</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
@@ -21616,119 +21616,127 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>99.6859</t>
+          <t>97.5962</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.3607</t>
+          <t>0.3496</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1194</t>
+          <t>0.1087</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.2744</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>67.29</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>54.54</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1794</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="BG76" t="inlineStr"/>
-      <c r="BH76" t="inlineStr"/>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="BG76" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21739,12 +21747,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -21769,7 +21777,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -21802,26 +21810,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>30.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>38.2</v>
+        <v>39.2</v>
       </c>
       <c r="R77" t="n">
         <v>38.7</v>
       </c>
       <c r="S77" t="n">
-        <v>71.7</v>
+        <v>95.5</v>
       </c>
       <c r="T77" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U77" t="n">
-        <v>82.7</v>
+        <v>43.4</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21835,7 +21843,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21877,27 +21885,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21907,67 +21915,67 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>99.9251</t>
+          <t>99.6859</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.3607</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.1194</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.3032</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>72.58</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.1484</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -22015,24 +22023,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>2026-08-04T00:40:00Z</t>
@@ -22045,26 +22053,26 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -22078,26 +22086,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>19.2</v>
+        <v>30.6</v>
       </c>
       <c r="Q78" t="n">
-        <v>53.1</v>
+        <v>38.2</v>
       </c>
       <c r="R78" t="n">
         <v>38.7</v>
       </c>
       <c r="S78" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T78" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U78" t="n">
-        <v>22.8</v>
+        <v>82.7</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22111,7 +22119,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22153,127 +22161,127 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>38.98</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>97.6971</t>
+          <t>99.9251</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1239</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.2616</t>
+          <t>0.3032</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>72.58</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1484</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4664</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1551</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr"/>
@@ -22291,24 +22299,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>2026-08-04T00:40:00Z</t>
@@ -22321,26 +22329,26 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>45.5</v>
+        <v>45.9</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22358,22 +22366,22 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="Q79" t="n">
-        <v>38.2</v>
+        <v>53.1</v>
       </c>
       <c r="R79" t="n">
         <v>38.7</v>
       </c>
       <c r="S79" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>60.3</v>
+        <v>22.8</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22387,7 +22395,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22412,7 +22420,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -22429,7 +22437,7 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
@@ -22444,112 +22452,112 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Contact streak: 8/20 over last 7 games</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>97.9931</t>
+          <t>97.6971</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1239</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.2616</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4664</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr"/>
@@ -22567,27 +22575,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-04T00:10:00Z</t>
+          <t>2026-08-04T00:40:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -22597,26 +22605,26 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -22630,26 +22638,26 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>41.4</v>
+        <v>24</v>
       </c>
       <c r="Q80" t="n">
-        <v>63.5</v>
+        <v>38.2</v>
       </c>
       <c r="R80" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S80" t="n">
-        <v>47.9</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T80" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U80" t="n">
-        <v>22.4</v>
+        <v>60.3</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -22663,7 +22671,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -22688,7 +22696,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -22705,134 +22713,134 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Contact streak: 8/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.3% barrel, 7.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>101.5247</t>
+          <t>97.9931</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.4145</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.5273</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1551</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr"/>
       <c r="BH80" t="inlineStr"/>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22843,47 +22851,47 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:10:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -22892,7 +22900,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -22906,58 +22914,62 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>36.7</v>
+        <v>41.4</v>
       </c>
       <c r="Q81" t="n">
-        <v>35</v>
+        <v>63.5</v>
       </c>
       <c r="R81" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S81" t="n">
-        <v>94.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T81" t="n">
         <v>50</v>
       </c>
       <c r="U81" t="n">
-        <v>14.1</v>
+        <v>22.4</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22977,12 +22989,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -22992,12 +23004,12 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.3% barrel, 7.3 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -23007,112 +23019,104 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>101.4575</t>
+          <t>101.5247</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.4245</t>
+          <t>0.4145</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>35.18</t>
+          <t>67.83</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>37.28</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.5273</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1532</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>26.93</t>
-        </is>
-      </c>
-      <c r="BG81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH81" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>24.98</t>
+        </is>
+      </c>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -23123,24 +23127,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>687462</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>2026-08-03T23:40:00Z</t>
@@ -23153,17 +23157,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>687075</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -23172,7 +23176,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>44.9</v>
+        <v>45.2</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23186,62 +23190,58 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>27.3</v>
+        <v>36.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>37.8</v>
+        <v>35</v>
       </c>
       <c r="R82" t="n">
         <v>41.1</v>
       </c>
       <c r="S82" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T82" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U82" t="n">
-        <v>40.7</v>
+        <v>14.1</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23261,27 +23261,27 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -23291,97 +23291,97 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>97.8032</t>
+          <t>101.4575</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.3937</t>
+          <t>0.4245</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.1556</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>35.18</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1285</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
@@ -23407,27 +23407,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>687462</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -23437,26 +23437,26 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>687075</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -23470,58 +23470,62 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>34.6</v>
+        <v>27.3</v>
       </c>
       <c r="Q83" t="n">
-        <v>42</v>
+        <v>37.8</v>
       </c>
       <c r="R83" t="n">
-        <v>51.8</v>
+        <v>41.1</v>
       </c>
       <c r="S83" t="n">
-        <v>76.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T83" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U83" t="n">
-        <v>5.7</v>
+        <v>40.7</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23541,27 +23545,27 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -23571,112 +23575,112 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>98.8983</t>
+          <t>97.8032</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.4214</t>
+          <t>0.3937</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1556</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.3475</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.1511</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.4071</t>
+          <t>0.3962</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -23687,22 +23691,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>808982</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -23717,26 +23721,26 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -23750,62 +23754,58 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>10.1</v>
+        <v>34.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>49.5</v>
+        <v>42</v>
       </c>
       <c r="R84" t="n">
-        <v>41.1</v>
+        <v>51.8</v>
       </c>
       <c r="S84" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T84" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U84" t="n">
-        <v>50.3</v>
+        <v>5.7</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23825,27 +23825,27 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -23855,112 +23855,112 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>39.21</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>86.82</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>96.5182</t>
+          <t>98.8983</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.4214</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.0919</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.3475</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>0.1354</t>
+          <t>0.1511</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>0.4568</t>
+          <t>0.4071</t>
         </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -23971,27 +23971,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>656537</t>
+          <t>808982</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -24001,26 +24001,26 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -24034,58 +24034,62 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>38.7</v>
+        <v>10.1</v>
       </c>
       <c r="Q85" t="n">
-        <v>23</v>
+        <v>49.5</v>
       </c>
       <c r="R85" t="n">
-        <v>71.3</v>
+        <v>41.1</v>
       </c>
       <c r="S85" t="n">
-        <v>52.4</v>
+        <v>95.5</v>
       </c>
       <c r="T85" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U85" t="n">
-        <v>18.3</v>
+        <v>50.3</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC85" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24105,27 +24109,27 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/10, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
@@ -24135,112 +24139,112 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>90.01</t>
+          <t>86.82</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>100.1694</t>
+          <t>96.5182</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>0.3957</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.0919</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>0.2999</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1354</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4568</t>
         </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI85" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ85" t="inlineStr"/>
@@ -24251,27 +24255,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>656537</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -24286,12 +24290,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -24314,62 +24318,58 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P86" t="n">
         <v>38.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="R86" t="n">
-        <v>51.8</v>
+        <v>71.3</v>
       </c>
       <c r="S86" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T86" t="n">
         <v>78</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24389,27 +24389,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/10, 1 HR</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24419,112 +24419,112 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>90.01</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>99.9647</t>
+          <t>100.1694</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4091</t>
+          <t>0.3957</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1771</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3121</t>
+          <t>0.2999</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>46.01</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.4101</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1507</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -25655,56 +25655,56 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>621020</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-04T01:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25718,26 +25718,26 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>18.9</v>
+        <v>38.7</v>
       </c>
       <c r="Q91" t="n">
-        <v>45.9</v>
+        <v>42</v>
       </c>
       <c r="R91" t="n">
-        <v>28.2</v>
+        <v>51.8</v>
       </c>
       <c r="S91" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T91" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U91" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -25793,12 +25793,12 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25808,12 +25808,12 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
@@ -25823,104 +25823,112 @@
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>43.39</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>89.73</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>98.428</t>
+          <t>99.9647</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4091</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1091</t>
+          <t>0.1771</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3121</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>71.46</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>46.01</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.4101</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1507</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>21.8</t>
-        </is>
-      </c>
-      <c r="BG91" t="inlineStr"/>
-      <c r="BH91" t="inlineStr"/>
+          <t>28.14</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH91" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -25931,56 +25939,56 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T01:40:00Z</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -25994,58 +26002,62 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>27.5</v>
+        <v>18.9</v>
       </c>
       <c r="Q92" t="n">
-        <v>23</v>
+        <v>45.9</v>
       </c>
       <c r="R92" t="n">
-        <v>71.3</v>
+        <v>28.2</v>
       </c>
       <c r="S92" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T92" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U92" t="n">
-        <v>52.8</v>
+        <v>23.4</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC92" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26065,27 +26077,27 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
@@ -26095,112 +26107,104 @@
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>34.38</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>98.5788</t>
+          <t>98.428</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>0.4014</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>0.1432</t>
+          <t>0.1091</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>71.46</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD92" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>16.01</t>
-        </is>
-      </c>
-      <c r="BG92" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH92" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
       <c r="BI92" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ92" t="inlineStr"/>
@@ -26211,27 +26215,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>682848</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Endy Rodriguez</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -26241,22 +26245,22 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>687075</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -26274,62 +26278,58 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>38.2</v>
+        <v>27.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>36.5</v>
+        <v>23</v>
       </c>
       <c r="R93" t="n">
-        <v>41.1</v>
+        <v>71.3</v>
       </c>
       <c r="S93" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T93" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U93" t="n">
-        <v>9.800000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26349,27 +26349,27 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
@@ -26379,112 +26379,112 @@
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>100.0463</t>
+          <t>98.5788</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>0.3656</t>
+          <t>0.4014</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1432</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>0.3113</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.1487</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD93" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG93" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI93" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ93" t="inlineStr"/>
@@ -26495,32 +26495,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>682848</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Endy Rodriguez</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-04T01:40:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -26530,12 +26530,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>687075</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -26544,7 +26544,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -26562,22 +26562,22 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>33.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q94" t="n">
-        <v>45.9</v>
+        <v>36.5</v>
       </c>
       <c r="R94" t="n">
-        <v>28.2</v>
+        <v>41.1</v>
       </c>
       <c r="S94" t="n">
         <v>59.8</v>
       </c>
       <c r="T94" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U94" t="n">
-        <v>16.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -26633,12 +26633,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -26648,12 +26648,12 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
@@ -26663,104 +26663,112 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>88.29</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>99.6998</t>
+          <t>100.0463</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.4005</t>
+          <t>0.3656</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3225</t>
+          <t>0.3113</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>74.52</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>45.02</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1798</t>
+          <t>0.1456</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.3962</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>21.8</t>
-        </is>
-      </c>
-      <c r="BG94" t="inlineStr"/>
-      <c r="BH94" t="inlineStr"/>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="BG94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH94" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -26771,47 +26779,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-04T01:40:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26820,7 +26828,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26834,58 +26842,62 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>23.3</v>
+        <v>33.6</v>
       </c>
       <c r="Q95" t="n">
-        <v>30.6</v>
+        <v>45.9</v>
       </c>
       <c r="R95" t="n">
-        <v>41.1</v>
+        <v>28.2</v>
       </c>
       <c r="S95" t="n">
-        <v>86.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T95" t="n">
         <v>80</v>
       </c>
       <c r="U95" t="n">
-        <v>40.3</v>
+        <v>16.6</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC95" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26905,12 +26917,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26920,12 +26932,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26935,112 +26947,104 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>88.29</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>98.8712</t>
+          <t>99.6998</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.3474</t>
+          <t>0.4005</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.3225</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>28.12</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1429</t>
+          <t>0.1798</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>18.65</t>
-        </is>
-      </c>
-      <c r="BG95" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH95" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -27051,22 +27055,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -27081,26 +27085,26 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>41.9</v>
+        <v>42.5</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -27114,62 +27118,58 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>8.699999999999999</v>
+        <v>23.3</v>
       </c>
       <c r="Q96" t="n">
-        <v>42</v>
+        <v>30.6</v>
       </c>
       <c r="R96" t="n">
-        <v>51.8</v>
+        <v>41.1</v>
       </c>
       <c r="S96" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T96" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U96" t="n">
-        <v>81.7</v>
+        <v>40.3</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27189,27 +27189,27 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
@@ -27219,112 +27219,112 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>86.28</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>96.3021</t>
+          <t>98.8712</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.3805</t>
+          <t>0.3474</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.0836</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.0977</t>
+          <t>0.1429</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>0.4101</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
-          <t>0.1507</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -27335,56 +27335,56 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -27398,26 +27398,26 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q97" t="n">
-        <v>53.1</v>
+        <v>42</v>
       </c>
       <c r="R97" t="n">
-        <v>38.7</v>
+        <v>51.8</v>
       </c>
       <c r="S97" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T97" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U97" t="n">
-        <v>33.9</v>
+        <v>81.7</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -27473,7 +27473,7 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
@@ -27483,17 +27483,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
@@ -27503,104 +27503,112 @@
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.04</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>85.02</t>
+          <t>86.28</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>96.4469</t>
+          <t>96.3021</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.3479</t>
+          <t>0.3805</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.0836</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.3115</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0977</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.4664</t>
+          <t>0.4101</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1507</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>25.59</t>
-        </is>
-      </c>
-      <c r="BG97" t="inlineStr"/>
-      <c r="BH97" t="inlineStr"/>
+          <t>28.14</t>
+        </is>
+      </c>
+      <c r="BG97" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH97" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27611,56 +27619,56 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:40:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27674,58 +27682,62 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q98" t="n">
-        <v>23</v>
+        <v>53.1</v>
       </c>
       <c r="R98" t="n">
-        <v>71.3</v>
+        <v>38.7</v>
       </c>
       <c r="S98" t="n">
-        <v>64.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T98" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>33.9</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC98" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27745,12 +27757,12 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -27760,12 +27772,12 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -27775,112 +27787,104 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>85.02</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>99.8568</t>
+          <t>96.4469</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.4246</t>
+          <t>0.3479</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.1544</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.3145</t>
+          <t>0.3115</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4664</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>16.01</t>
-        </is>
-      </c>
-      <c r="BG98" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH98" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
+          <t>25.59</t>
+        </is>
+      </c>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27891,27 +27895,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>676609</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>José Caballero</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-03T23:05:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -27921,22 +27925,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -27954,26 +27958,26 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>8.199999999999999</v>
+        <v>28.8</v>
       </c>
       <c r="Q99" t="n">
-        <v>55.6</v>
+        <v>23</v>
       </c>
       <c r="R99" t="n">
-        <v>77.7</v>
+        <v>71.3</v>
       </c>
       <c r="S99" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T99" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U99" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27987,7 +27991,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -28025,27 +28029,27 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/22, 0 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -28055,97 +28059,97 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>84.46</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>96.3388</t>
+          <t>99.8568</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.3362</t>
+          <t>0.4246</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.1544</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.2836</t>
+          <t>0.3145</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.4864</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr">
@@ -28155,12 +28159,12 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
@@ -28171,24 +28175,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>2026-08-03T23:05:00Z</t>
@@ -28201,17 +28205,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -28220,7 +28224,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -28238,22 +28242,22 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q100" t="n">
-        <v>35.4</v>
+        <v>55.6</v>
       </c>
       <c r="R100" t="n">
         <v>77.7</v>
       </c>
       <c r="S100" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T100" t="n">
         <v>50</v>
       </c>
       <c r="U100" t="n">
-        <v>25.8</v>
+        <v>43.2</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -28267,7 +28271,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -28305,27 +28309,27 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
@@ -28335,97 +28339,97 @@
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>84.46</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>98.6916</t>
+          <t>96.3388</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.3362</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.1087</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>0.2965</t>
+          <t>0.2836</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>15.42</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>39.64</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="BD100" t="inlineStr">
         <is>
-          <t>0.3546</t>
+          <t>0.4864</t>
         </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr">
@@ -28451,47 +28455,47 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>672386</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-04T00:10:00Z</t>
+          <t>2026-08-03T23:05:00Z</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -28514,62 +28518,58 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>26.5</v>
+        <v>15</v>
       </c>
       <c r="Q101" t="n">
-        <v>47.1</v>
+        <v>35.4</v>
       </c>
       <c r="R101" t="n">
-        <v>27.6</v>
+        <v>77.7</v>
       </c>
       <c r="S101" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T101" t="n">
         <v>50</v>
       </c>
       <c r="U101" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28589,12 +28589,12 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -28604,119 +28604,127 @@
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>100.4736</t>
+          <t>98.6916</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>0.3876</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.2965</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>71.73</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>0.1138</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.3546</t>
         </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>38.45</t>
-        </is>
-      </c>
-      <c r="BG101" t="inlineStr"/>
-      <c r="BH101" t="inlineStr"/>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BG101" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH101" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="BI101" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ101" t="inlineStr"/>
@@ -28727,24 +28735,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>672386</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>2026-08-04T00:10:00Z</t>
@@ -28757,17 +28765,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -28776,7 +28784,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>39.6</v>
+        <v>41.6</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -28794,22 +28802,22 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>15.2</v>
+        <v>26.5</v>
       </c>
       <c r="Q102" t="n">
-        <v>63.5</v>
+        <v>47.1</v>
       </c>
       <c r="R102" t="n">
         <v>27.6</v>
       </c>
       <c r="S102" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T102" t="n">
         <v>50</v>
       </c>
       <c r="U102" t="n">
-        <v>13</v>
+        <v>28.2</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -28823,7 +28831,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -28865,12 +28873,12 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -28880,112 +28888,112 @@
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.3% barrel, 7.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>85.45</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>97.2544</t>
+          <t>100.4736</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.3448</t>
+          <t>0.3876</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.2818</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.73</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>27.26</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1138</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.5273</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
@@ -29003,47 +29011,47 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:10:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -29052,7 +29060,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>39.2</v>
+        <v>39.6</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -29066,26 +29074,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Projected Lineup, Good Environment, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>15.2</v>
       </c>
       <c r="Q103" t="n">
-        <v>50.7</v>
+        <v>63.5</v>
       </c>
       <c r="R103" t="n">
-        <v>71.3</v>
+        <v>27.6</v>
       </c>
       <c r="S103" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T103" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U103" t="n">
-        <v>10.1</v>
+        <v>13</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29099,7 +29107,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29141,12 +29149,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29156,12 +29164,12 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.3% barrel, 7.3 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
@@ -29171,112 +29179,104 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>84.01</t>
+          <t>85.45</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>95.6367</t>
+          <t>97.2544</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.3448</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.0813</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.2996</t>
+          <t>0.2818</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>44.94</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.0925</t>
+          <t>0.1588</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.5273</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.1794</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>27.53</t>
-        </is>
-      </c>
-      <c r="BG103" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH103" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
+          <t>24.98</t>
+        </is>
+      </c>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -29287,27 +29287,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>665804</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -29317,26 +29317,26 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29350,26 +29350,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="Q104" t="n">
-        <v>42</v>
+        <v>50.7</v>
       </c>
       <c r="R104" t="n">
-        <v>51.8</v>
+        <v>71.3</v>
       </c>
       <c r="S104" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T104" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U104" t="n">
-        <v>27</v>
+        <v>10.1</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29425,12 +29425,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29440,12 +29440,12 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29455,112 +29455,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.03</t>
+          <t>84.01</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>97.668</t>
+          <t>95.6367</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3412</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1224</t>
+          <t>0.0813</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.2996</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>43.56</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1469</t>
+          <t>0.0925</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.4101</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1507</t>
+          <t>0.1794</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
